--- a/dummy_loto6.xlsx
+++ b/dummy_loto6.xlsx
@@ -482,22 +482,22 @@
         <v>43892</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E2" t="n">
+        <v>31</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38</v>
+      </c>
+      <c r="H2" t="n">
         <v>39</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H2" t="n">
-        <v>43</v>
       </c>
     </row>
     <row r="3">
@@ -508,19 +508,19 @@
         <v>43899</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
         <v>19</v>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G3" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H3" t="n">
         <v>42</v>
@@ -534,19 +534,19 @@
         <v>43906</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" t="n">
         <v>17</v>
       </c>
-      <c r="E4" t="n">
-        <v>34</v>
-      </c>
       <c r="F4" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H4" t="n">
         <v>43</v>
@@ -560,22 +560,22 @@
         <v>43913</v>
       </c>
       <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F5" t="n">
         <v>22</v>
       </c>
-      <c r="D5" t="n">
-        <v>25</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
+        <v>24</v>
+      </c>
+      <c r="H5" t="n">
         <v>26</v>
-      </c>
-      <c r="F5" t="n">
-        <v>34</v>
-      </c>
-      <c r="G5" t="n">
-        <v>38</v>
-      </c>
-      <c r="H5" t="n">
-        <v>43</v>
       </c>
     </row>
     <row r="6">
@@ -586,22 +586,22 @@
         <v>43920</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H6" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -612,22 +612,24 @@
         <v>43927</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
-      </c>
-      <c r="E7" t="n">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>無効</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H7" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -638,22 +640,22 @@
         <v>43934</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G8" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="H8" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
@@ -664,19 +666,19 @@
         <v>43941</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G9" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H9" t="n">
         <v>41</v>
@@ -690,22 +692,22 @@
         <v>43948</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
         <v>39</v>
       </c>
       <c r="H10" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11">
@@ -716,22 +718,22 @@
         <v>43955</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F11" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G11" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
@@ -742,22 +744,22 @@
         <v>43962</v>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G12" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H12" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
@@ -768,22 +770,22 @@
         <v>43969</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="H13" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -794,22 +796,22 @@
         <v>43976</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E14" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F14" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G14" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="H14" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
@@ -820,22 +822,22 @@
         <v>43983</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F15" t="n">
         <v>23</v>
       </c>
       <c r="G15" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="H15" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16">
@@ -846,22 +848,22 @@
         <v>43990</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G16" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H16" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17">
@@ -872,22 +874,20 @@
         <v>43997</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>27</v>
-      </c>
-      <c r="F17" t="n">
-        <v>29</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -898,22 +898,22 @@
         <v>44004</v>
       </c>
       <c r="C18" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E18" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F18" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G18" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H18" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -924,22 +924,22 @@
         <v>44011</v>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F19" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="G19" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -950,22 +950,22 @@
         <v>44018</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="F20" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G20" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H20" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21">
@@ -976,22 +976,22 @@
         <v>44025</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E21" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F21" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G21" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H21" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22">
@@ -1002,22 +1002,22 @@
         <v>44032</v>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F22" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G22" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H22" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23">
@@ -1028,22 +1028,22 @@
         <v>44039</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D23" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E23" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F23" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G23" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H23" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24">
@@ -1054,22 +1054,22 @@
         <v>44046</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E24" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F24" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G24" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H24" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25">
@@ -1080,22 +1080,22 @@
         <v>44053</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E25" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F25" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G25" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H25" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26">
@@ -1106,22 +1106,22 @@
         <v>44060</v>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E26" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F26" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G26" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="H26" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27">
@@ -1132,22 +1132,22 @@
         <v>44067</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E27" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F27" t="n">
         <v>27</v>
       </c>
       <c r="G27" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H27" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28">
@@ -1158,22 +1158,22 @@
         <v>44074</v>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E28" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F28" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G28" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H28" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29">
@@ -1184,22 +1184,22 @@
         <v>44081</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E29" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F29" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="G29" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H29" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30">
@@ -1210,22 +1210,22 @@
         <v>44088</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="E30" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F30" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G30" t="n">
+        <v>38</v>
+      </c>
+      <c r="H30" t="n">
         <v>39</v>
-      </c>
-      <c r="H30" t="n">
-        <v>41</v>
       </c>
     </row>
     <row r="31">
@@ -1236,22 +1236,22 @@
         <v>44095</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F31" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G31" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="H31" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32">
@@ -1262,22 +1262,22 @@
         <v>44102</v>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E32" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F32" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G32" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H32" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33">
@@ -1288,22 +1288,22 @@
         <v>44109</v>
       </c>
       <c r="C33" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>13</v>
+      </c>
+      <c r="F33" t="n">
         <v>17</v>
       </c>
-      <c r="E33" t="n">
-        <v>27</v>
-      </c>
-      <c r="F33" t="n">
-        <v>35</v>
-      </c>
       <c r="G33" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="H33" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34">
@@ -1314,22 +1314,22 @@
         <v>44116</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="E34" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="F34" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="G34" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="H34" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35">
@@ -1340,22 +1340,22 @@
         <v>44123</v>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D35" t="n">
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F35" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G35" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H35" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36">
@@ -1366,22 +1366,22 @@
         <v>44130</v>
       </c>
       <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
         <v>13</v>
       </c>
-      <c r="D36" t="n">
-        <v>21</v>
-      </c>
       <c r="E36" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F36" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G36" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H36" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37">
@@ -1392,22 +1392,22 @@
         <v>44137</v>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D37" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E37" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="F37" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G37" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H37" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38">
@@ -1418,22 +1418,22 @@
         <v>44144</v>
       </c>
       <c r="C38" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E38" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F38" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G38" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H38" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39">
@@ -1444,22 +1444,22 @@
         <v>44151</v>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E39" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F39" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="G39" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="H39" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40">
@@ -1470,22 +1470,22 @@
         <v>44158</v>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E40" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F40" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G40" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H40" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41">
@@ -1496,22 +1496,22 @@
         <v>44165</v>
       </c>
       <c r="C41" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E41" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F41" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G41" t="n">
+        <v>36</v>
+      </c>
+      <c r="H41" t="n">
         <v>37</v>
-      </c>
-      <c r="H41" t="n">
-        <v>41</v>
       </c>
     </row>
     <row r="42">
@@ -1522,22 +1522,22 @@
         <v>44172</v>
       </c>
       <c r="C42" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D42" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E42" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F42" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G42" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H42" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43">
@@ -1548,22 +1548,22 @@
         <v>44179</v>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E43" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F43" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G43" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="H43" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44">
@@ -1574,22 +1574,22 @@
         <v>44186</v>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E44" t="n">
         <v>26</v>
       </c>
       <c r="F44" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G44" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H44" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45">
@@ -1600,22 +1600,22 @@
         <v>44193</v>
       </c>
       <c r="C45" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D45" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E45" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F45" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G45" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H45" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46">
@@ -1626,22 +1626,22 @@
         <v>44200</v>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D46" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E46" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F46" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G46" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H46" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47">
@@ -1652,22 +1652,22 @@
         <v>44207</v>
       </c>
       <c r="C47" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F47" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G47" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H47" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48">
@@ -1678,22 +1678,22 @@
         <v>44214</v>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E48" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F48" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G48" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H48" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49">
@@ -1704,22 +1704,22 @@
         <v>44221</v>
       </c>
       <c r="C49" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E49" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F49" t="n">
         <v>26</v>
       </c>
       <c r="G49" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H49" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50">
@@ -1730,22 +1730,22 @@
         <v>44228</v>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D50" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E50" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F50" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G50" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H50" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="51">
@@ -1756,22 +1756,22 @@
         <v>44235</v>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E51" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F51" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G51" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="H51" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52">
@@ -1785,19 +1785,19 @@
         <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F52" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G52" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H52" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53">
@@ -1811,19 +1811,19 @@
         <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E53" t="n">
         <v>18</v>
       </c>
       <c r="F53" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G53" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H53" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="54">
@@ -1834,22 +1834,22 @@
         <v>44256</v>
       </c>
       <c r="C54" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D54" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E54" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F54" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G54" t="n">
+        <v>31</v>
+      </c>
+      <c r="H54" t="n">
         <v>36</v>
-      </c>
-      <c r="H54" t="n">
-        <v>38</v>
       </c>
     </row>
     <row r="55">
@@ -1860,22 +1860,22 @@
         <v>44263</v>
       </c>
       <c r="C55" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E55" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F55" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G55" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H55" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56">
@@ -1886,22 +1886,22 @@
         <v>44270</v>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G56" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H56" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="57">
@@ -1912,22 +1912,22 @@
         <v>44277</v>
       </c>
       <c r="C57" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E57" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F57" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="G57" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="H57" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58">
@@ -1938,22 +1938,22 @@
         <v>44284</v>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F58" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="G58" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H58" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="59">
@@ -1964,22 +1964,22 @@
         <v>44291</v>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D59" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E59" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F59" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G59" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="H59" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="60">
@@ -1990,22 +1990,22 @@
         <v>44298</v>
       </c>
       <c r="C60" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" t="n">
+        <v>8</v>
+      </c>
+      <c r="E60" t="n">
         <v>10</v>
       </c>
-      <c r="D60" t="n">
-        <v>14</v>
-      </c>
-      <c r="E60" t="n">
-        <v>20</v>
-      </c>
       <c r="F60" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G60" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="H60" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61">
@@ -2016,19 +2016,19 @@
         <v>44305</v>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D61" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E61" t="n">
+        <v>12</v>
+      </c>
+      <c r="F61" t="n">
         <v>16</v>
       </c>
-      <c r="F61" t="n">
-        <v>25</v>
-      </c>
       <c r="G61" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="H61" t="n">
         <v>29</v>
@@ -2042,22 +2042,22 @@
         <v>44312</v>
       </c>
       <c r="C62" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D62" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E62" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F62" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="G62" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H62" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="63">
@@ -2068,22 +2068,22 @@
         <v>44319</v>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E63" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F63" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G63" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H63" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="64">
@@ -2094,22 +2094,22 @@
         <v>44326</v>
       </c>
       <c r="C64" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D64" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G64" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H64" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
     </row>
     <row r="65">
@@ -2123,19 +2123,19 @@
         <v>3</v>
       </c>
       <c r="D65" t="n">
+        <v>5</v>
+      </c>
+      <c r="E65" t="n">
+        <v>17</v>
+      </c>
+      <c r="F65" t="n">
         <v>18</v>
       </c>
-      <c r="E65" t="n">
-        <v>22</v>
-      </c>
-      <c r="F65" t="n">
-        <v>31</v>
-      </c>
       <c r="G65" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H65" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66">
@@ -2146,22 +2146,22 @@
         <v>44340</v>
       </c>
       <c r="C66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D66" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E66" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F66" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G66" t="n">
+        <v>36</v>
+      </c>
+      <c r="H66" t="n">
         <v>37</v>
-      </c>
-      <c r="H66" t="n">
-        <v>43</v>
       </c>
     </row>
     <row r="67">
@@ -2172,22 +2172,22 @@
         <v>44347</v>
       </c>
       <c r="C67" t="n">
+        <v>8</v>
+      </c>
+      <c r="D67" t="n">
+        <v>11</v>
+      </c>
+      <c r="E67" t="n">
         <v>17</v>
       </c>
-      <c r="D67" t="n">
-        <v>21</v>
-      </c>
-      <c r="E67" t="n">
+      <c r="F67" t="n">
         <v>22</v>
       </c>
-      <c r="F67" t="n">
+      <c r="G67" t="n">
         <v>26</v>
       </c>
-      <c r="G67" t="n">
-        <v>30</v>
-      </c>
       <c r="H67" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="68">
@@ -2198,22 +2198,22 @@
         <v>44354</v>
       </c>
       <c r="C68" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D68" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E68" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F68" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G68" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H68" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
     </row>
     <row r="69">
@@ -2224,22 +2224,22 @@
         <v>44361</v>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E69" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F69" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="G69" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H69" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="70">
@@ -2250,22 +2250,22 @@
         <v>44368</v>
       </c>
       <c r="C70" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D70" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E70" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F70" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G70" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H70" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="71">
@@ -2276,22 +2276,22 @@
         <v>44375</v>
       </c>
       <c r="C71" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D71" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E71" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F71" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G71" t="n">
         <v>34</v>
       </c>
       <c r="H71" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="72">
@@ -2305,19 +2305,19 @@
         <v>2</v>
       </c>
       <c r="D72" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F72" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G72" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H72" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="73">
@@ -2328,22 +2328,22 @@
         <v>44389</v>
       </c>
       <c r="C73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D73" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E73" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F73" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G73" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H73" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="74">
@@ -2354,22 +2354,22 @@
         <v>44396</v>
       </c>
       <c r="C74" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D74" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E74" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F74" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G74" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H74" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="75">
@@ -2380,22 +2380,22 @@
         <v>44403</v>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D75" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E75" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F75" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G75" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H75" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="76">
@@ -2406,22 +2406,22 @@
         <v>44410</v>
       </c>
       <c r="C76" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D76" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E76" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F76" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G76" t="n">
+        <v>29</v>
+      </c>
+      <c r="H76" t="n">
         <v>31</v>
-      </c>
-      <c r="H76" t="n">
-        <v>42</v>
       </c>
     </row>
     <row r="77">
@@ -2432,22 +2432,22 @@
         <v>44417</v>
       </c>
       <c r="C77" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E77" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F77" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G77" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="H77" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="78">
@@ -2458,22 +2458,22 @@
         <v>44424</v>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E78" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F78" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="G78" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H78" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="79">
@@ -2487,16 +2487,16 @@
         <v>2</v>
       </c>
       <c r="D79" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E79" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F79" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G79" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H79" t="n">
         <v>43</v>
@@ -2510,22 +2510,22 @@
         <v>44438</v>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D80" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E80" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="F80" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G80" t="n">
         <v>36</v>
       </c>
       <c r="H80" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="81">
@@ -2536,22 +2536,22 @@
         <v>44445</v>
       </c>
       <c r="C81" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D81" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E81" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F81" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G81" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H81" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="82">
@@ -2562,22 +2562,22 @@
         <v>44452</v>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D82" t="n">
+        <v>7</v>
+      </c>
+      <c r="E82" t="n">
+        <v>12</v>
+      </c>
+      <c r="F82" t="n">
         <v>18</v>
       </c>
-      <c r="E82" t="n">
-        <v>19</v>
-      </c>
-      <c r="F82" t="n">
-        <v>27</v>
-      </c>
       <c r="G82" t="n">
+        <v>28</v>
+      </c>
+      <c r="H82" t="n">
         <v>29</v>
-      </c>
-      <c r="H82" t="n">
-        <v>39</v>
       </c>
     </row>
     <row r="83">
@@ -2588,22 +2588,22 @@
         <v>44459</v>
       </c>
       <c r="C83" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E83" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F83" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G83" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H83" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="84">
@@ -2617,19 +2617,19 @@
         <v>8</v>
       </c>
       <c r="D84" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E84" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F84" t="n">
+        <v>22</v>
+      </c>
+      <c r="G84" t="n">
         <v>28</v>
       </c>
-      <c r="G84" t="n">
-        <v>32</v>
-      </c>
       <c r="H84" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="85">
@@ -2640,22 +2640,22 @@
         <v>44473</v>
       </c>
       <c r="C85" t="n">
+        <v>5</v>
+      </c>
+      <c r="D85" t="n">
         <v>10</v>
       </c>
-      <c r="D85" t="n">
-        <v>14</v>
-      </c>
       <c r="E85" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F85" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G85" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H85" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="86">
@@ -2666,19 +2666,19 @@
         <v>44480</v>
       </c>
       <c r="C86" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D86" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E86" t="n">
         <v>28</v>
       </c>
       <c r="F86" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G86" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H86" t="n">
         <v>42</v>
@@ -2695,19 +2695,19 @@
         <v>4</v>
       </c>
       <c r="D87" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E87" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F87" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G87" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H87" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="88">
@@ -2718,22 +2718,22 @@
         <v>44494</v>
       </c>
       <c r="C88" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F88" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G88" t="n">
         <v>34</v>
       </c>
       <c r="H88" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="89">
@@ -2744,22 +2744,22 @@
         <v>44501</v>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D89" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E89" t="n">
+        <v>10</v>
+      </c>
+      <c r="F89" t="n">
         <v>12</v>
       </c>
-      <c r="F89" t="n">
-        <v>26</v>
-      </c>
       <c r="G89" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="H89" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90">
@@ -2770,22 +2770,22 @@
         <v>44508</v>
       </c>
       <c r="C90" t="n">
+        <v>7</v>
+      </c>
+      <c r="D90" t="n">
+        <v>10</v>
+      </c>
+      <c r="E90" t="n">
         <v>12</v>
       </c>
-      <c r="D90" t="n">
-        <v>13</v>
-      </c>
-      <c r="E90" t="n">
-        <v>24</v>
-      </c>
       <c r="F90" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G90" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H90" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
     </row>
     <row r="91">
@@ -2796,22 +2796,22 @@
         <v>44515</v>
       </c>
       <c r="C91" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D91" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E91" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F91" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="G91" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="H91" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="92">
@@ -2822,22 +2822,22 @@
         <v>44522</v>
       </c>
       <c r="C92" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D92" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E92" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F92" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G92" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H92" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="93">
@@ -2848,22 +2848,22 @@
         <v>44529</v>
       </c>
       <c r="C93" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D93" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E93" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F93" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G93" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="H93" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
     </row>
     <row r="94">
@@ -2874,22 +2874,22 @@
         <v>44536</v>
       </c>
       <c r="C94" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D94" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E94" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F94" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G94" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="H94" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="95">
@@ -2900,22 +2900,22 @@
         <v>44543</v>
       </c>
       <c r="C95" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D95" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E95" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F95" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G95" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H95" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="96">
@@ -2926,22 +2926,22 @@
         <v>44550</v>
       </c>
       <c r="C96" t="n">
+        <v>4</v>
+      </c>
+      <c r="D96" t="n">
+        <v>6</v>
+      </c>
+      <c r="E96" t="n">
         <v>11</v>
       </c>
-      <c r="D96" t="n">
-        <v>21</v>
-      </c>
-      <c r="E96" t="n">
-        <v>25</v>
-      </c>
       <c r="F96" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G96" t="n">
+        <v>35</v>
+      </c>
+      <c r="H96" t="n">
         <v>36</v>
-      </c>
-      <c r="H96" t="n">
-        <v>42</v>
       </c>
     </row>
     <row r="97">
@@ -2952,22 +2952,22 @@
         <v>44557</v>
       </c>
       <c r="C97" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D97" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E97" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F97" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G97" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H97" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="98">
@@ -2978,22 +2978,22 @@
         <v>44564</v>
       </c>
       <c r="C98" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D98" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E98" t="n">
+        <v>18</v>
+      </c>
+      <c r="F98" t="n">
+        <v>24</v>
+      </c>
+      <c r="G98" t="n">
         <v>27</v>
       </c>
-      <c r="F98" t="n">
-        <v>32</v>
-      </c>
-      <c r="G98" t="n">
+      <c r="H98" t="n">
         <v>36</v>
-      </c>
-      <c r="H98" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="99">
@@ -3004,22 +3004,22 @@
         <v>44571</v>
       </c>
       <c r="C99" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D99" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E99" t="n">
         <v>11</v>
       </c>
       <c r="F99" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G99" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="H99" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="100">
@@ -3033,19 +3033,19 @@
         <v>7</v>
       </c>
       <c r="D100" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E100" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F100" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="G100" t="n">
+        <v>33</v>
+      </c>
+      <c r="H100" t="n">
         <v>34</v>
-      </c>
-      <c r="H100" t="n">
-        <v>41</v>
       </c>
     </row>
     <row r="101">
@@ -3056,19 +3056,19 @@
         <v>44585</v>
       </c>
       <c r="C101" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D101" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E101" t="n">
+        <v>19</v>
+      </c>
+      <c r="F101" t="n">
         <v>21</v>
       </c>
-      <c r="F101" t="n">
-        <v>23</v>
-      </c>
       <c r="G101" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H101" t="n">
         <v>43</v>
@@ -3082,19 +3082,19 @@
         <v>44592</v>
       </c>
       <c r="C102" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D102" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E102" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F102" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G102" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="H102" t="n">
         <v>42</v>
@@ -3108,22 +3108,22 @@
         <v>44599</v>
       </c>
       <c r="C103" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D103" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E103" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F103" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G103" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="H103" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="104">
@@ -3134,22 +3134,22 @@
         <v>44606</v>
       </c>
       <c r="C104" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D104" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E104" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F104" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="G104" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H104" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="105">
@@ -3160,22 +3160,22 @@
         <v>44613</v>
       </c>
       <c r="C105" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D105" t="n">
+        <v>5</v>
+      </c>
+      <c r="E105" t="n">
         <v>18</v>
       </c>
-      <c r="E105" t="n">
-        <v>26</v>
-      </c>
       <c r="F105" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G105" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H105" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="106">
@@ -3186,22 +3186,22 @@
         <v>44620</v>
       </c>
       <c r="C106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D106" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E106" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F106" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G106" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="H106" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="107">
@@ -3212,22 +3212,22 @@
         <v>44627</v>
       </c>
       <c r="C107" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D107" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E107" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F107" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G107" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H107" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="108">
@@ -3238,22 +3238,22 @@
         <v>44634</v>
       </c>
       <c r="C108" t="n">
+        <v>3</v>
+      </c>
+      <c r="D108" t="n">
         <v>5</v>
       </c>
-      <c r="D108" t="n">
-        <v>20</v>
-      </c>
       <c r="E108" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F108" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G108" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H108" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109">
@@ -3264,22 +3264,22 @@
         <v>44641</v>
       </c>
       <c r="C109" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D109" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E109" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F109" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G109" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H109" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="110">
@@ -3290,22 +3290,22 @@
         <v>44648</v>
       </c>
       <c r="C110" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D110" t="n">
         <v>11</v>
       </c>
       <c r="E110" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F110" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G110" t="n">
+        <v>32</v>
+      </c>
+      <c r="H110" t="n">
         <v>35</v>
-      </c>
-      <c r="H110" t="n">
-        <v>39</v>
       </c>
     </row>
     <row r="111">
@@ -3316,19 +3316,19 @@
         <v>44655</v>
       </c>
       <c r="C111" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D111" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="E111" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F111" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G111" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H111" t="n">
         <v>43</v>
@@ -3345,19 +3345,19 @@
         <v>1</v>
       </c>
       <c r="D112" t="n">
+        <v>6</v>
+      </c>
+      <c r="E112" t="n">
         <v>7</v>
       </c>
-      <c r="E112" t="n">
-        <v>17</v>
-      </c>
       <c r="F112" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G112" t="n">
         <v>25</v>
       </c>
       <c r="H112" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="113">
@@ -3368,22 +3368,22 @@
         <v>44669</v>
       </c>
       <c r="C113" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D113" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E113" t="n">
+        <v>17</v>
+      </c>
+      <c r="F113" t="n">
         <v>21</v>
       </c>
-      <c r="F113" t="n">
-        <v>35</v>
-      </c>
       <c r="G113" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="H113" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="114">
@@ -3397,19 +3397,19 @@
         <v>6</v>
       </c>
       <c r="D114" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E114" t="n">
         <v>15</v>
       </c>
       <c r="F114" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G114" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H114" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="115">
@@ -3420,22 +3420,22 @@
         <v>44683</v>
       </c>
       <c r="C115" t="n">
+        <v>2</v>
+      </c>
+      <c r="D115" t="n">
+        <v>4</v>
+      </c>
+      <c r="E115" t="n">
+        <v>7</v>
+      </c>
+      <c r="F115" t="n">
+        <v>11</v>
+      </c>
+      <c r="G115" t="n">
         <v>13</v>
       </c>
-      <c r="D115" t="n">
-        <v>16</v>
-      </c>
-      <c r="E115" t="n">
-        <v>22</v>
-      </c>
-      <c r="F115" t="n">
-        <v>32</v>
-      </c>
-      <c r="G115" t="n">
-        <v>33</v>
-      </c>
       <c r="H115" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="116">
@@ -3449,19 +3449,19 @@
         <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E116" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F116" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G116" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H116" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="117">
@@ -3472,22 +3472,22 @@
         <v>44697</v>
       </c>
       <c r="C117" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D117" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E117" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F117" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G117" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H117" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="118">
@@ -3498,22 +3498,22 @@
         <v>44704</v>
       </c>
       <c r="C118" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D118" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E118" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F118" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G118" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H118" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="119">
@@ -3524,22 +3524,22 @@
         <v>44711</v>
       </c>
       <c r="C119" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D119" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E119" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F119" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G119" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H119" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="120">
@@ -3550,22 +3550,22 @@
         <v>44718</v>
       </c>
       <c r="C120" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D120" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E120" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F120" t="n">
         <v>30</v>
       </c>
       <c r="G120" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H120" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="121">
@@ -3576,22 +3576,22 @@
         <v>44725</v>
       </c>
       <c r="C121" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D121" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E121" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F121" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G121" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H121" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="122">
@@ -3602,22 +3602,22 @@
         <v>44732</v>
       </c>
       <c r="C122" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D122" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E122" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F122" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G122" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H122" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="123">
@@ -3628,22 +3628,22 @@
         <v>44739</v>
       </c>
       <c r="C123" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D123" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E123" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F123" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G123" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H123" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="124">
@@ -3654,22 +3654,22 @@
         <v>44746</v>
       </c>
       <c r="C124" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D124" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E124" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F124" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G124" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="H124" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="125">
@@ -3680,22 +3680,22 @@
         <v>44753</v>
       </c>
       <c r="C125" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D125" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E125" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F125" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G125" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H125" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
     </row>
     <row r="126">
@@ -3706,22 +3706,22 @@
         <v>44760</v>
       </c>
       <c r="C126" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D126" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E126" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F126" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G126" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H126" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
     </row>
     <row r="127">
@@ -3732,22 +3732,22 @@
         <v>44767</v>
       </c>
       <c r="C127" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D127" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E127" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F127" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G127" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H127" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="128">
@@ -3758,22 +3758,22 @@
         <v>44774</v>
       </c>
       <c r="C128" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D128" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E128" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F128" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="G128" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H128" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="129">
@@ -3784,22 +3784,22 @@
         <v>44781</v>
       </c>
       <c r="C129" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D129" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E129" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F129" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G129" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H129" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="130">
@@ -3810,19 +3810,19 @@
         <v>44788</v>
       </c>
       <c r="C130" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D130" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E130" t="n">
+        <v>20</v>
+      </c>
+      <c r="F130" t="n">
         <v>21</v>
       </c>
-      <c r="F130" t="n">
+      <c r="G130" t="n">
         <v>32</v>
-      </c>
-      <c r="G130" t="n">
-        <v>37</v>
       </c>
       <c r="H130" t="n">
         <v>41</v>
@@ -3836,22 +3836,22 @@
         <v>44795</v>
       </c>
       <c r="C131" t="n">
+        <v>3</v>
+      </c>
+      <c r="D131" t="n">
         <v>15</v>
       </c>
-      <c r="D131" t="n">
-        <v>19</v>
-      </c>
       <c r="E131" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F131" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G131" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H131" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="132">
@@ -3862,22 +3862,22 @@
         <v>44802</v>
       </c>
       <c r="C132" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D132" t="n">
         <v>9</v>
       </c>
       <c r="E132" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F132" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G132" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H132" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="133">
@@ -3888,22 +3888,22 @@
         <v>44809</v>
       </c>
       <c r="C133" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D133" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E133" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F133" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G133" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H133" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="134">
@@ -3914,22 +3914,22 @@
         <v>44816</v>
       </c>
       <c r="C134" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D134" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E134" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F134" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="G134" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H134" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="135">
@@ -3940,22 +3940,22 @@
         <v>44823</v>
       </c>
       <c r="C135" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D135" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E135" t="n">
+        <v>13</v>
+      </c>
+      <c r="F135" t="n">
         <v>22</v>
       </c>
-      <c r="F135" t="n">
-        <v>25</v>
-      </c>
       <c r="G135" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H135" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="136">
@@ -3966,22 +3966,22 @@
         <v>44830</v>
       </c>
       <c r="C136" t="n">
+        <v>4</v>
+      </c>
+      <c r="D136" t="n">
+        <v>8</v>
+      </c>
+      <c r="E136" t="n">
         <v>9</v>
       </c>
-      <c r="D136" t="n">
-        <v>17</v>
-      </c>
-      <c r="E136" t="n">
-        <v>19</v>
-      </c>
       <c r="F136" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G136" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="H136" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="137">
@@ -3992,22 +3992,22 @@
         <v>44837</v>
       </c>
       <c r="C137" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D137" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E137" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F137" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G137" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H137" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="138">
@@ -4018,22 +4018,22 @@
         <v>44844</v>
       </c>
       <c r="C138" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D138" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E138" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F138" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G138" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H138" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="139">
@@ -4044,22 +4044,22 @@
         <v>44851</v>
       </c>
       <c r="C139" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D139" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="E139" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F139" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G139" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H139" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="140">
@@ -4070,22 +4070,22 @@
         <v>44858</v>
       </c>
       <c r="C140" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D140" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E140" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F140" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G140" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H140" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="141">
@@ -4096,22 +4096,22 @@
         <v>44865</v>
       </c>
       <c r="C141" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D141" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E141" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F141" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="G141" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="H141" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
     </row>
     <row r="142">
@@ -4125,19 +4125,19 @@
         <v>1</v>
       </c>
       <c r="D142" t="n">
+        <v>2</v>
+      </c>
+      <c r="E142" t="n">
         <v>9</v>
       </c>
-      <c r="E142" t="n">
-        <v>22</v>
-      </c>
       <c r="F142" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="G142" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="H142" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="143">
@@ -4148,22 +4148,22 @@
         <v>44879</v>
       </c>
       <c r="C143" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D143" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E143" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F143" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G143" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H143" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="144">
@@ -4174,19 +4174,19 @@
         <v>44886</v>
       </c>
       <c r="C144" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D144" t="n">
         <v>14</v>
       </c>
       <c r="E144" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F144" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G144" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H144" t="n">
         <v>38</v>
@@ -4200,22 +4200,22 @@
         <v>44893</v>
       </c>
       <c r="C145" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D145" t="n">
         <v>13</v>
       </c>
       <c r="E145" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F145" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G145" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H145" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="146">
@@ -4226,22 +4226,22 @@
         <v>44900</v>
       </c>
       <c r="C146" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D146" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E146" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F146" t="n">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="G146" t="n">
+        <v>24</v>
+      </c>
+      <c r="H146" t="n">
         <v>42</v>
-      </c>
-      <c r="H146" t="n">
-        <v>43</v>
       </c>
     </row>
     <row r="147">
@@ -4252,22 +4252,22 @@
         <v>44907</v>
       </c>
       <c r="C147" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D147" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E147" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F147" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G147" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H147" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="148">
@@ -4278,22 +4278,22 @@
         <v>44914</v>
       </c>
       <c r="C148" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D148" t="n">
+        <v>7</v>
+      </c>
+      <c r="E148" t="n">
         <v>9</v>
       </c>
-      <c r="E148" t="n">
-        <v>13</v>
-      </c>
       <c r="F148" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G148" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H148" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="149">
@@ -4304,22 +4304,22 @@
         <v>44921</v>
       </c>
       <c r="C149" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D149" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E149" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F149" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G149" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="H149" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="150">
@@ -4330,19 +4330,19 @@
         <v>44928</v>
       </c>
       <c r="C150" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D150" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E150" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F150" t="n">
+        <v>30</v>
+      </c>
+      <c r="G150" t="n">
         <v>32</v>
-      </c>
-      <c r="G150" t="n">
-        <v>38</v>
       </c>
       <c r="H150" t="n">
         <v>43</v>
@@ -4356,22 +4356,22 @@
         <v>44935</v>
       </c>
       <c r="C151" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D151" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E151" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F151" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G151" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H151" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="152">
@@ -4382,22 +4382,22 @@
         <v>44942</v>
       </c>
       <c r="C152" t="n">
+        <v>5</v>
+      </c>
+      <c r="D152" t="n">
         <v>12</v>
       </c>
-      <c r="D152" t="n">
+      <c r="E152" t="n">
+        <v>18</v>
+      </c>
+      <c r="F152" t="n">
+        <v>20</v>
+      </c>
+      <c r="G152" t="n">
         <v>24</v>
       </c>
-      <c r="E152" t="n">
-        <v>25</v>
-      </c>
-      <c r="F152" t="n">
-        <v>28</v>
-      </c>
-      <c r="G152" t="n">
-        <v>35</v>
-      </c>
       <c r="H152" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="153">
@@ -4408,22 +4408,22 @@
         <v>44949</v>
       </c>
       <c r="C153" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D153" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E153" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F153" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G153" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H153" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="154">
@@ -4434,22 +4434,22 @@
         <v>44956</v>
       </c>
       <c r="C154" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D154" t="n">
         <v>12</v>
       </c>
       <c r="E154" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F154" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G154" t="n">
         <v>32</v>
       </c>
       <c r="H154" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="155">
@@ -4460,22 +4460,22 @@
         <v>44963</v>
       </c>
       <c r="C155" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D155" t="n">
+        <v>8</v>
+      </c>
+      <c r="E155" t="n">
+        <v>16</v>
+      </c>
+      <c r="F155" t="n">
         <v>24</v>
       </c>
-      <c r="E155" t="n">
-        <v>30</v>
-      </c>
-      <c r="F155" t="n">
-        <v>34</v>
-      </c>
       <c r="G155" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="H155" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="156">
@@ -4486,22 +4486,22 @@
         <v>44970</v>
       </c>
       <c r="C156" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="D156" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E156" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F156" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G156" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H156" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="157">
@@ -4512,22 +4512,22 @@
         <v>44977</v>
       </c>
       <c r="C157" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D157" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E157" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F157" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G157" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H157" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="158">
@@ -4538,22 +4538,22 @@
         <v>44984</v>
       </c>
       <c r="C158" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D158" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E158" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F158" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G158" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H158" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="159">
@@ -4564,22 +4564,22 @@
         <v>44991</v>
       </c>
       <c r="C159" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D159" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E159" t="n">
         <v>13</v>
       </c>
       <c r="F159" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G159" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H159" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="160">
@@ -4590,22 +4590,22 @@
         <v>44998</v>
       </c>
       <c r="C160" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D160" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E160" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F160" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G160" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H160" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="161">
@@ -4616,22 +4616,22 @@
         <v>45005</v>
       </c>
       <c r="C161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D161" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E161" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F161" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G161" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H161" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="162">
@@ -4642,22 +4642,22 @@
         <v>45012</v>
       </c>
       <c r="C162" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D162" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E162" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="F162" t="n">
+        <v>30</v>
+      </c>
+      <c r="G162" t="n">
         <v>31</v>
       </c>
-      <c r="G162" t="n">
-        <v>38</v>
-      </c>
       <c r="H162" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="163">
@@ -4668,22 +4668,22 @@
         <v>45019</v>
       </c>
       <c r="C163" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D163" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E163" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F163" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G163" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H163" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="164">
@@ -4694,22 +4694,22 @@
         <v>45026</v>
       </c>
       <c r="C164" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D164" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E164" t="n">
         <v>15</v>
       </c>
       <c r="F164" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G164" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="H164" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="165">
@@ -4720,22 +4720,22 @@
         <v>45033</v>
       </c>
       <c r="C165" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" t="n">
+        <v>9</v>
+      </c>
+      <c r="E165" t="n">
         <v>13</v>
       </c>
-      <c r="D165" t="n">
-        <v>15</v>
-      </c>
-      <c r="E165" t="n">
-        <v>16</v>
-      </c>
       <c r="F165" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G165" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H165" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="166">
@@ -4746,22 +4746,22 @@
         <v>45040</v>
       </c>
       <c r="C166" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D166" t="n">
         <v>20</v>
       </c>
       <c r="E166" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F166" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G166" t="n">
         <v>38</v>
       </c>
       <c r="H166" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="167">
@@ -4772,22 +4772,22 @@
         <v>45047</v>
       </c>
       <c r="C167" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D167" t="n">
+        <v>7</v>
+      </c>
+      <c r="E167" t="n">
         <v>19</v>
       </c>
-      <c r="E167" t="n">
-        <v>20</v>
-      </c>
       <c r="F167" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G167" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H167" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="168">
@@ -4798,22 +4798,22 @@
         <v>45054</v>
       </c>
       <c r="C168" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D168" t="n">
+        <v>5</v>
+      </c>
+      <c r="E168" t="n">
+        <v>14</v>
+      </c>
+      <c r="F168" t="n">
         <v>15</v>
       </c>
-      <c r="E168" t="n">
-        <v>21</v>
-      </c>
-      <c r="F168" t="n">
-        <v>37</v>
-      </c>
       <c r="G168" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H168" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="169">
@@ -4824,22 +4824,22 @@
         <v>45061</v>
       </c>
       <c r="C169" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D169" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E169" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F169" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="G169" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H169" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="170">
@@ -4850,22 +4850,22 @@
         <v>45068</v>
       </c>
       <c r="C170" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D170" t="n">
+        <v>6</v>
+      </c>
+      <c r="E170" t="n">
         <v>16</v>
       </c>
-      <c r="E170" t="n">
+      <c r="F170" t="n">
         <v>20</v>
       </c>
-      <c r="F170" t="n">
-        <v>27</v>
-      </c>
       <c r="G170" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="H170" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="171">
@@ -4876,22 +4876,22 @@
         <v>45075</v>
       </c>
       <c r="C171" t="n">
+        <v>9</v>
+      </c>
+      <c r="D171" t="n">
         <v>12</v>
       </c>
-      <c r="D171" t="n">
-        <v>20</v>
-      </c>
       <c r="E171" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F171" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="G171" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="H171" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="172">
@@ -4902,22 +4902,22 @@
         <v>45082</v>
       </c>
       <c r="C172" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D172" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E172" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F172" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G172" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H172" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="173">
@@ -4928,22 +4928,22 @@
         <v>45089</v>
       </c>
       <c r="C173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D173" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E173" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F173" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G173" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H173" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="174">
@@ -4954,22 +4954,22 @@
         <v>45096</v>
       </c>
       <c r="C174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D174" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E174" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F174" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G174" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H174" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="175">
@@ -4980,22 +4980,22 @@
         <v>45103</v>
       </c>
       <c r="C175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D175" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E175" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F175" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G175" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="H175" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="176">
@@ -5006,22 +5006,22 @@
         <v>45110</v>
       </c>
       <c r="C176" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D176" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E176" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F176" t="n">
+        <v>29</v>
+      </c>
+      <c r="G176" t="n">
         <v>38</v>
       </c>
-      <c r="G176" t="n">
-        <v>39</v>
-      </c>
       <c r="H176" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="177">
@@ -5032,22 +5032,22 @@
         <v>45117</v>
       </c>
       <c r="C177" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D177" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E177" t="n">
+        <v>24</v>
+      </c>
+      <c r="F177" t="n">
+        <v>26</v>
+      </c>
+      <c r="G177" t="n">
         <v>32</v>
       </c>
-      <c r="F177" t="n">
-        <v>40</v>
-      </c>
-      <c r="G177" t="n">
-        <v>41</v>
-      </c>
       <c r="H177" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="178">
@@ -5058,22 +5058,22 @@
         <v>45124</v>
       </c>
       <c r="C178" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D178" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E178" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F178" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G178" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H178" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="179">
@@ -5084,22 +5084,22 @@
         <v>45131</v>
       </c>
       <c r="C179" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D179" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E179" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F179" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G179" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H179" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="180">
@@ -5110,22 +5110,22 @@
         <v>45138</v>
       </c>
       <c r="C180" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D180" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E180" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F180" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G180" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H180" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="181">
@@ -5136,22 +5136,22 @@
         <v>45145</v>
       </c>
       <c r="C181" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D181" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E181" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F181" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G181" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H181" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="182">
@@ -5162,22 +5162,22 @@
         <v>45152</v>
       </c>
       <c r="C182" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D182" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E182" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F182" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G182" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H182" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="183">
@@ -5188,22 +5188,22 @@
         <v>45159</v>
       </c>
       <c r="C183" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D183" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E183" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F183" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G183" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="H183" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="184">
@@ -5214,22 +5214,22 @@
         <v>45166</v>
       </c>
       <c r="C184" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D184" t="n">
         <v>10</v>
       </c>
       <c r="E184" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F184" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G184" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H184" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
     </row>
     <row r="185">
@@ -5240,19 +5240,19 @@
         <v>45173</v>
       </c>
       <c r="C185" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D185" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E185" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F185" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G185" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H185" t="n">
         <v>42</v>
@@ -5266,19 +5266,19 @@
         <v>45180</v>
       </c>
       <c r="C186" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D186" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E186" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F186" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G186" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="H186" t="n">
         <v>40</v>
@@ -5292,22 +5292,22 @@
         <v>45187</v>
       </c>
       <c r="C187" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D187" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E187" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F187" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G187" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H187" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="188">
@@ -5318,22 +5318,22 @@
         <v>45194</v>
       </c>
       <c r="C188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D188" t="n">
+        <v>4</v>
+      </c>
+      <c r="E188" t="n">
         <v>7</v>
       </c>
-      <c r="E188" t="n">
-        <v>22</v>
-      </c>
       <c r="F188" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="G188" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="H188" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="189">
@@ -5344,22 +5344,22 @@
         <v>45201</v>
       </c>
       <c r="C189" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D189" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E189" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F189" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="G189" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H189" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="190">
@@ -5370,22 +5370,22 @@
         <v>45208</v>
       </c>
       <c r="C190" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D190" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E190" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F190" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G190" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H190" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="191">
@@ -5396,22 +5396,22 @@
         <v>45215</v>
       </c>
       <c r="C191" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D191" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E191" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F191" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="G191" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H191" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="192">
@@ -5422,19 +5422,19 @@
         <v>45222</v>
       </c>
       <c r="C192" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D192" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E192" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F192" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G192" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H192" t="n">
         <v>43</v>
@@ -5448,22 +5448,22 @@
         <v>45229</v>
       </c>
       <c r="C193" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D193" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E193" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F193" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="G193" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="H193" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="194">
@@ -5477,19 +5477,19 @@
         <v>2</v>
       </c>
       <c r="D194" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="E194" t="n">
+        <v>6</v>
+      </c>
+      <c r="F194" t="n">
+        <v>9</v>
+      </c>
+      <c r="G194" t="n">
         <v>24</v>
       </c>
-      <c r="F194" t="n">
-        <v>25</v>
-      </c>
-      <c r="G194" t="n">
-        <v>26</v>
-      </c>
       <c r="H194" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="195">
@@ -5500,22 +5500,22 @@
         <v>45243</v>
       </c>
       <c r="C195" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D195" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E195" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F195" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="G195" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="H195" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="196">
@@ -5526,22 +5526,22 @@
         <v>45250</v>
       </c>
       <c r="C196" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D196" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E196" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F196" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="G196" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H196" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="197">
@@ -5552,22 +5552,22 @@
         <v>45257</v>
       </c>
       <c r="C197" t="n">
+        <v>3</v>
+      </c>
+      <c r="D197" t="n">
         <v>8</v>
       </c>
-      <c r="D197" t="n">
-        <v>17</v>
-      </c>
       <c r="E197" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F197" t="n">
         <v>22</v>
       </c>
       <c r="G197" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H197" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="198">
@@ -5578,22 +5578,22 @@
         <v>45264</v>
       </c>
       <c r="C198" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D198" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E198" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F198" t="n">
         <v>24</v>
       </c>
       <c r="G198" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H198" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="199">
@@ -5604,13 +5604,13 @@
         <v>45271</v>
       </c>
       <c r="C199" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D199" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E199" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F199" t="n">
         <v>32</v>
@@ -5619,7 +5619,7 @@
         <v>34</v>
       </c>
       <c r="H199" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="200">
@@ -5630,22 +5630,22 @@
         <v>45278</v>
       </c>
       <c r="C200" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D200" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E200" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="F200" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="G200" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H200" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="201">
@@ -5659,19 +5659,19 @@
         <v>1</v>
       </c>
       <c r="D201" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E201" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F201" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G201" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="H201" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
